--- a/data/pack/eu/colza.xlsx
+++ b/data/pack/eu/colza.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Datos" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fuente y licencia" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Datos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Fuente y licencia" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K286"/>
+  <dimension ref="A1:K287"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16164,6 +16164,61 @@
         </is>
       </c>
       <c r="K286" t="inlineStr">
+        <is>
+          <t>Source: European Commission (Agri-food data portal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>colza</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Colza</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="D287" t="inlineStr">
+        <is>
+          <t>2026-10-18</t>
+        </is>
+      </c>
+      <c r="E287" t="n">
+        <v>476.14</v>
+      </c>
+      <c r="F287" t="inlineStr">
+        <is>
+          <t>tonelada</t>
+        </is>
+      </c>
+      <c r="G287" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H287" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="I287" t="inlineStr">
+        <is>
+          <t>European Commission — Agri-food Data Portal (DG AGRI)</t>
+        </is>
+      </c>
+      <c r="J287" t="inlineStr">
+        <is>
+          <t>EU-REUSE-2011-833</t>
+        </is>
+      </c>
+      <c r="K287" t="inlineStr">
         <is>
           <t>Source: European Commission (Agri-food data portal)</t>
         </is>
@@ -16267,7 +16322,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-11</t>
+          <t>2026-10-18</t>
         </is>
       </c>
     </row>
@@ -16278,7 +16333,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="9">
@@ -16373,7 +16428,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-15</t>
+          <t>2026-10-22</t>
         </is>
       </c>
     </row>

--- a/data/pack/eu/colza.xlsx
+++ b/data/pack/eu/colza.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K287"/>
+  <dimension ref="A1:K288"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -16219,6 +16219,61 @@
         </is>
       </c>
       <c r="K287" t="inlineStr">
+        <is>
+          <t>Source: European Commission (Agri-food data portal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>colza</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Colza</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>EU</t>
+        </is>
+      </c>
+      <c r="D288" t="inlineStr">
+        <is>
+          <t>2026-10-25</t>
+        </is>
+      </c>
+      <c r="E288" t="n">
+        <v>499.75</v>
+      </c>
+      <c r="F288" t="inlineStr">
+        <is>
+          <t>tonelada</t>
+        </is>
+      </c>
+      <c r="G288" t="inlineStr">
+        <is>
+          <t>EUR</t>
+        </is>
+      </c>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="I288" t="inlineStr">
+        <is>
+          <t>European Commission — Agri-food Data Portal (DG AGRI)</t>
+        </is>
+      </c>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>EU-REUSE-2011-833</t>
+        </is>
+      </c>
+      <c r="K288" t="inlineStr">
         <is>
           <t>Source: European Commission (Agri-food data portal)</t>
         </is>
@@ -16322,7 +16377,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-18</t>
+          <t>2026-10-25</t>
         </is>
       </c>
     </row>
@@ -16333,7 +16388,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="9">
@@ -16428,7 +16483,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>2026-10-22</t>
+          <t>2026-10-29</t>
         </is>
       </c>
     </row>
